--- a/exports/trend_1d/TIINDIA_full_report.xlsx
+++ b/exports/trend_1d/TIINDIA_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q51"/>
+  <dimension ref="A1:U51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>14.87</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>43123</v>
+        <v>43124</v>
       </c>
       <c r="H2" t="n">
-        <v>273.7</v>
+        <v>260.75</v>
       </c>
       <c r="I2" t="n">
         <v>265.0535019353192</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K2" t="n">
-        <v>-5.78</v>
+        <v>-10.24</v>
       </c>
       <c r="L2" t="n">
         <v>25.75</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>18.98</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>43187</v>
+        <v>43192</v>
       </c>
       <c r="H3" t="n">
-        <v>222.4</v>
+        <v>254.05</v>
       </c>
       <c r="I3" t="n">
         <v>251.7401314278054</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="K3" t="n">
-        <v>14.71</v>
+        <v>2.57</v>
       </c>
       <c r="L3" t="n">
         <v>13.14</v>
@@ -612,7 +647,7 @@
         <v>3.63</v>
       </c>
       <c r="N3" t="n">
-        <v>3.65</v>
+        <v>14.23</v>
       </c>
       <c r="O3" t="n">
         <v>-4.73</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>19.22</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>43242</v>
+        <v>43243</v>
       </c>
       <c r="H4" t="n">
-        <v>221.75</v>
+        <v>215.3</v>
       </c>
       <c r="I4" t="n">
         <v>215.6807435434776</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K4" t="n">
-        <v>-12.71</v>
+        <v>-15.25</v>
       </c>
       <c r="L4" t="n">
-        <v>13.4</v>
+        <v>15.37</v>
       </c>
       <c r="M4" t="n">
         <v>2.04</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>12.37</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>43269</v>
+        <v>43270</v>
       </c>
       <c r="H5" t="n">
-        <v>235.1</v>
+        <v>239.15</v>
       </c>
       <c r="I5" t="n">
         <v>238.3141172556692</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K5" t="n">
-        <v>-9.199999999999999</v>
+        <v>-11.08</v>
       </c>
       <c r="L5" t="n">
-        <v>11.15</v>
+        <v>11.47</v>
       </c>
       <c r="M5" t="n">
         <v>1.72</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>11.97</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>43300</v>
+        <v>43301</v>
       </c>
       <c r="H6" t="n">
-        <v>226.75</v>
+        <v>223.8</v>
       </c>
       <c r="I6" t="n">
         <v>224.0730019213769</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K6" t="n">
-        <v>-5.19</v>
+        <v>-6.42</v>
       </c>
       <c r="L6" t="n">
         <v>8.529999999999999</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>12.91</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>43326</v>
+        <v>43328</v>
       </c>
       <c r="H7" t="n">
-        <v>245.95</v>
+        <v>258</v>
       </c>
       <c r="I7" t="n">
         <v>252.6990283582973</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K7" t="n">
-        <v>-9.9</v>
+        <v>-15.28</v>
       </c>
       <c r="L7" t="n">
         <v>16.18</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>13.97</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>43669</v>
+        <v>43670</v>
       </c>
       <c r="H8" t="n">
-        <v>384.2</v>
+        <v>376.5</v>
       </c>
       <c r="I8" t="n">
         <v>378.5912600198017</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K8" t="n">
-        <v>48.91</v>
+        <v>45.93</v>
       </c>
       <c r="L8" t="n">
         <v>5.29</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>228</v>
+        <v>229</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>12</v>
+      </c>
+      <c r="U8" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>12.06</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>43728</v>
+        <v>43731</v>
       </c>
       <c r="H9" t="n">
-        <v>345.45</v>
+        <v>365.8</v>
       </c>
       <c r="I9" t="n">
         <v>363.0175500959151</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K9" t="n">
-        <v>8.25</v>
+        <v>2.84</v>
       </c>
       <c r="L9" t="n">
         <v>3.59</v>
@@ -954,7 +1061,7 @@
         <v>3.22</v>
       </c>
       <c r="N9" t="n">
-        <v>4.62</v>
+        <v>5.89</v>
       </c>
       <c r="O9" t="n">
         <v>-2</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>14.01</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>43858</v>
+        <v>43859</v>
       </c>
       <c r="H10" t="n">
-        <v>512.4</v>
+        <v>486.8</v>
       </c>
       <c r="I10" t="n">
         <v>487.4230690554537</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K10" t="n">
-        <v>40.08</v>
+        <v>33.08</v>
       </c>
       <c r="L10" t="n">
         <v>5.39</v>
@@ -1011,7 +1130,7 @@
         <v>2.33</v>
       </c>
       <c r="N10" t="n">
-        <v>2.78</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
         <v>5.89</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>11.33</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>43881</v>
+        <v>43885</v>
       </c>
       <c r="H11" t="n">
-        <v>505.8</v>
+        <v>544.5</v>
       </c>
       <c r="I11" t="n">
         <v>541.9706521927053</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.9</v>
+        <v>-11.85</v>
       </c>
       <c r="L11" t="n">
-        <v>10.72</v>
+        <v>15.45</v>
       </c>
       <c r="M11" t="n">
         <v>1.73</v>
       </c>
       <c r="N11" t="n">
-        <v>7.01</v>
+        <v>7.65</v>
       </c>
       <c r="O11" t="n">
         <v>-5</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>14.73</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>43901</v>
+        <v>43902</v>
       </c>
       <c r="H12" t="n">
-        <v>501.95</v>
+        <v>481.5</v>
       </c>
       <c r="I12" t="n">
         <v>488.8496237963002</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K12" t="n">
-        <v>-7.81</v>
+        <v>-11.57</v>
       </c>
       <c r="L12" t="n">
-        <v>8.91</v>
+        <v>14.6</v>
       </c>
       <c r="M12" t="n">
         <v>3.97</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>16.46</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43950</v>
+        <v>43951</v>
       </c>
       <c r="H13" t="n">
-        <v>354.3</v>
+        <v>373.25</v>
       </c>
       <c r="I13" t="n">
         <v>371.1437117067622</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K13" t="n">
-        <v>26.42</v>
+        <v>22.48</v>
       </c>
       <c r="L13" t="n">
         <v>2.78</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>20.29</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43977</v>
+        <v>43978</v>
       </c>
       <c r="H14" t="n">
-        <v>310.95</v>
+        <v>309.55</v>
       </c>
       <c r="I14" t="n">
         <v>310.1325253051227</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K14" t="n">
-        <v>-16.69</v>
+        <v>-17.07</v>
       </c>
       <c r="L14" t="n">
-        <v>17.21</v>
+        <v>17.9</v>
       </c>
       <c r="M14" t="n">
         <v>1.41</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>16.62</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43979</v>
+        <v>43980</v>
       </c>
       <c r="H15" t="n">
-        <v>340.45</v>
+        <v>367.5</v>
       </c>
       <c r="I15" t="n">
         <v>361.0105755697538</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>-9.98</v>
+        <v>-18.72</v>
       </c>
       <c r="L15" t="n">
-        <v>10</v>
+        <v>19.85</v>
       </c>
       <c r="M15" t="n">
         <v>2.25</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
+        <v>3</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
         <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>18.41</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44095</v>
+        <v>44096</v>
       </c>
       <c r="H16" t="n">
-        <v>621.25</v>
+        <v>575.1</v>
       </c>
       <c r="I16" t="n">
         <v>602.073919267016</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K16" t="n">
-        <v>69.05</v>
+        <v>56.49</v>
       </c>
       <c r="L16" t="n">
         <v>6.67</v>
@@ -1353,7 +1544,7 @@
         <v>3.59</v>
       </c>
       <c r="N16" t="n">
-        <v>4.46</v>
+        <v>7.43</v>
       </c>
       <c r="O16" t="n">
         <v>7.95</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>17.84</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44130</v>
+        <v>44131</v>
       </c>
       <c r="H17" t="n">
-        <v>622.55</v>
+        <v>649.35</v>
       </c>
       <c r="I17" t="n">
         <v>645.2394550559603</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K17" t="n">
-        <v>-8.25</v>
+        <v>-12.91</v>
       </c>
       <c r="L17" t="n">
         <v>13.53</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>15.26</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44218</v>
+        <v>44221</v>
       </c>
       <c r="H18" t="n">
-        <v>823.25</v>
+        <v>781.3</v>
       </c>
       <c r="I18" t="n">
         <v>788.2795788354932</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K18" t="n">
-        <v>26.78</v>
+        <v>20.32</v>
       </c>
       <c r="L18" t="n">
         <v>3.97</v>
@@ -1467,7 +1682,7 @@
         <v>1.73</v>
       </c>
       <c r="N18" t="n">
-        <v>3.05</v>
+        <v>5.1</v>
       </c>
       <c r="O18" t="n">
         <v>4.3</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>12.91</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44232</v>
+        <v>44235</v>
       </c>
       <c r="H19" t="n">
-        <v>858.3</v>
+        <v>905.35</v>
       </c>
       <c r="I19" t="n">
         <v>863.6768334934296</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K19" t="n">
-        <v>-9.859999999999999</v>
+        <v>-15.88</v>
       </c>
       <c r="L19" t="n">
-        <v>11.86</v>
+        <v>18.67</v>
       </c>
       <c r="M19" t="n">
         <v>3.44</v>
       </c>
       <c r="N19" t="n">
-        <v>4.71</v>
+        <v>5.48</v>
       </c>
       <c r="O19" t="n">
         <v>-5.1</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>15.47</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44364</v>
+        <v>44365</v>
       </c>
       <c r="H20" t="n">
-        <v>1244.2</v>
+        <v>1192.05</v>
       </c>
       <c r="I20" t="n">
         <v>1197.760996945041</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K20" t="n">
-        <v>37.43</v>
+        <v>31.67</v>
       </c>
       <c r="L20" t="n">
         <v>4.46</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>21.37</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44412</v>
+        <v>44413</v>
       </c>
       <c r="H21" t="n">
-        <v>1172.95</v>
+        <v>1197.5</v>
       </c>
       <c r="I21" t="n">
         <v>1195.308217228469</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K21" t="n">
-        <v>1.6</v>
+        <v>-0.46</v>
       </c>
       <c r="L21" t="n">
         <v>9.48</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>13.59</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44474</v>
+        <v>44475</v>
       </c>
       <c r="H22" t="n">
-        <v>1328.75</v>
+        <v>1289.15</v>
       </c>
       <c r="I22" t="n">
         <v>1326.760526572144</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K22" t="n">
-        <v>10.96</v>
+        <v>7.65</v>
       </c>
       <c r="L22" t="n">
         <v>6.47</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>15.52</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>44501</v>
+        <v>44502</v>
       </c>
       <c r="H23" t="n">
-        <v>1445.4</v>
+        <v>1657.2</v>
       </c>
       <c r="I23" t="n">
         <v>1486.036206899408</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K23" t="n">
-        <v>-12.12</v>
+        <v>-28.55</v>
       </c>
       <c r="L23" t="n">
-        <v>13.42</v>
+        <v>31.87</v>
       </c>
       <c r="M23" t="n">
         <v>2.27</v>
       </c>
       <c r="N23" t="n">
-        <v>3.5</v>
+        <v>14.65</v>
       </c>
       <c r="O23" t="n">
         <v>-2.98</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>19.89</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H24" t="n">
-        <v>1783</v>
+        <v>1714.6</v>
       </c>
       <c r="I24" t="n">
         <v>1716.473522783386</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K24" t="n">
-        <v>7.59</v>
+        <v>3.46</v>
       </c>
       <c r="L24" t="n">
         <v>12.93</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>12.77</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>44655</v>
+        <v>44656</v>
       </c>
       <c r="H25" t="n">
-        <v>1612.55</v>
+        <v>1699.8</v>
       </c>
       <c r="I25" t="n">
         <v>1679.807724040397</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K25" t="n">
-        <v>5.95</v>
+        <v>0.86</v>
       </c>
       <c r="L25" t="n">
         <v>8.83</v>
@@ -1866,7 +2165,7 @@
         <v>2.67</v>
       </c>
       <c r="N25" t="n">
-        <v>4.96</v>
+        <v>5.41</v>
       </c>
       <c r="O25" t="n">
         <v>-3.84</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>13.33</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>44691</v>
+        <v>44692</v>
       </c>
       <c r="H26" t="n">
-        <v>1804</v>
+        <v>1666.6</v>
       </c>
       <c r="I26" t="n">
         <v>1697.165461879043</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K26" t="n">
-        <v>6.13</v>
+        <v>-1.95</v>
       </c>
       <c r="L26" t="n">
         <v>4.99</v>
       </c>
       <c r="M26" t="n">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="N26" t="n">
-        <v>5.35</v>
+        <v>7.62</v>
       </c>
       <c r="O26" t="n">
         <v>5.41</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>16.48</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>44739</v>
+        <v>44740</v>
       </c>
       <c r="H27" t="n">
-        <v>1632.8</v>
+        <v>1753.8</v>
       </c>
       <c r="I27" t="n">
         <v>1651.534022294412</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K27" t="n">
-        <v>2.03</v>
+        <v>-5.23</v>
       </c>
       <c r="L27" t="n">
         <v>8.42</v>
@@ -1980,7 +2303,7 @@
         <v>1.97</v>
       </c>
       <c r="N27" t="n">
-        <v>5.5</v>
+        <v>7.41</v>
       </c>
       <c r="O27" t="n">
         <v>-7.62</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>14.33</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44876</v>
+        <v>44879</v>
       </c>
       <c r="H28" t="n">
-        <v>2573.15</v>
+        <v>2508.7</v>
       </c>
       <c r="I28" t="n">
         <v>2557.631847137058</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="K28" t="n">
-        <v>46.72</v>
+        <v>43.04</v>
       </c>
       <c r="L28" t="n">
         <v>7.41</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>6</v>
+      </c>
+      <c r="U28" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>17.08</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44896</v>
+        <v>44897</v>
       </c>
       <c r="H29" t="n">
-        <v>2818.1</v>
+        <v>2933.3</v>
       </c>
       <c r="I29" t="n">
         <v>2913.042585072222</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K29" t="n">
-        <v>-12.33</v>
+        <v>-16.93</v>
       </c>
       <c r="L29" t="n">
-        <v>13.16</v>
+        <v>18.53</v>
       </c>
       <c r="M29" t="n">
         <v>1.97</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>15.41</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44939</v>
+        <v>44942</v>
       </c>
       <c r="H30" t="n">
-        <v>2652.8</v>
+        <v>2619.7</v>
       </c>
       <c r="I30" t="n">
         <v>2634.28475817687</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K30" t="n">
-        <v>-9.56</v>
+        <v>-10.69</v>
       </c>
       <c r="L30" t="n">
         <v>11.53</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>10.47</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44984</v>
+        <v>44985</v>
       </c>
       <c r="H31" t="n">
-        <v>2660.5</v>
+        <v>2771.8</v>
       </c>
       <c r="I31" t="n">
         <v>2675.518231894571</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.56</v>
+        <v>-5.81</v>
       </c>
       <c r="L31" t="n">
-        <v>4.78</v>
+        <v>9.25</v>
       </c>
       <c r="M31" t="n">
         <v>0.89</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>14.03</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45146</v>
+        <v>45147</v>
       </c>
       <c r="H32" t="n">
-        <v>3004.05</v>
+        <v>2932.85</v>
       </c>
       <c r="I32" t="n">
         <v>2985.909779633164</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K32" t="n">
-        <v>8.380000000000001</v>
+        <v>5.81</v>
       </c>
       <c r="L32" t="n">
         <v>12.62</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>109</v>
+        <v>110</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>6</v>
+      </c>
+      <c r="U32" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>10.67</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45170</v>
+        <v>45173</v>
       </c>
       <c r="H33" t="n">
-        <v>2988.15</v>
+        <v>3054.45</v>
       </c>
       <c r="I33" t="n">
         <v>3031.563516571591</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.89</v>
+        <v>-4.15</v>
       </c>
       <c r="L33" t="n">
-        <v>3.37</v>
+        <v>4.33</v>
       </c>
       <c r="M33" t="n">
         <v>4.93</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>10.06</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45195</v>
+        <v>45196</v>
       </c>
       <c r="H34" t="n">
-        <v>3181.3</v>
+        <v>3099.4</v>
       </c>
       <c r="I34" t="n">
         <v>3143.220917258987</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K34" t="n">
-        <v>4.15</v>
+        <v>1.47</v>
       </c>
       <c r="L34" t="n">
         <v>3.03</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>13.72</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45232</v>
+        <v>45233</v>
       </c>
       <c r="H35" t="n">
-        <v>3138.2</v>
+        <v>3199.35</v>
       </c>
       <c r="I35" t="n">
         <v>3179.332180258018</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K35" t="n">
-        <v>-1.25</v>
+        <v>-3.22</v>
       </c>
       <c r="L35" t="n">
-        <v>3.12</v>
+        <v>4.12</v>
       </c>
       <c r="M35" t="n">
         <v>1.25</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>9.91</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45329</v>
+        <v>45330</v>
       </c>
       <c r="H36" t="n">
-        <v>3600.45</v>
+        <v>3507.45</v>
       </c>
       <c r="I36" t="n">
         <v>3552.959211464848</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K36" t="n">
-        <v>12.54</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="L36" t="n">
         <v>2.8</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>15.6</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45412</v>
+        <v>45414</v>
       </c>
       <c r="H37" t="n">
-        <v>3742.6</v>
+        <v>3791</v>
       </c>
       <c r="I37" t="n">
         <v>3758.54853369175</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K37" t="n">
-        <v>-6.7</v>
+        <v>-8.08</v>
       </c>
       <c r="L37" t="n">
         <v>9.619999999999999</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>4</v>
+      </c>
+      <c r="U37" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -2586,25 +3041,25 @@
         <v>7.8</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45442</v>
+        <v>45443</v>
       </c>
       <c r="H38" t="n">
-        <v>3699.95</v>
+        <v>3576.85</v>
       </c>
       <c r="I38" t="n">
         <v>3646.776059558336</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K38" t="n">
-        <v>-2.4</v>
+        <v>-5.65</v>
       </c>
       <c r="L38" t="n">
-        <v>4.51</v>
+        <v>7.68</v>
       </c>
       <c r="M38" t="n">
-        <v>1.88</v>
+        <v>5.4</v>
       </c>
       <c r="N38" t="n">
         <v>4.51</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>12.47</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45453</v>
+        <v>45454</v>
       </c>
       <c r="H39" t="n">
-        <v>3959.55</v>
+        <v>4064.55</v>
       </c>
       <c r="I39" t="n">
         <v>4022.747687234603</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K39" t="n">
-        <v>-10.7</v>
+        <v>-13.63</v>
       </c>
       <c r="L39" t="n">
-        <v>11.94</v>
+        <v>14.36</v>
       </c>
       <c r="M39" t="n">
         <v>3.43</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>12.64</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45601</v>
+        <v>45602</v>
       </c>
       <c r="H40" t="n">
-        <v>4183.3</v>
+        <v>4096.8</v>
       </c>
       <c r="I40" t="n">
         <v>4097.712200231457</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K40" t="n">
-        <v>2.92</v>
+        <v>0.79</v>
       </c>
       <c r="L40" t="n">
         <v>5.04</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>6</v>
+      </c>
+      <c r="U40" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>14.37</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="H41" t="n">
-        <v>2714.6</v>
+        <v>2882.05</v>
       </c>
       <c r="I41" t="n">
         <v>2812.275442714407</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K41" t="n">
-        <v>33.74</v>
+        <v>29.65</v>
       </c>
       <c r="L41" t="n">
         <v>2.94</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>5</v>
+      </c>
+      <c r="U41" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -2814,25 +3317,25 @@
         <v>15.54</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45751</v>
+        <v>45754</v>
       </c>
       <c r="H42" t="n">
-        <v>2637.25</v>
+        <v>2578.95</v>
       </c>
       <c r="I42" t="n">
         <v>2597.812609733622</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K42" t="n">
-        <v>-8.49</v>
+        <v>-10.52</v>
       </c>
       <c r="L42" t="n">
-        <v>9.140000000000001</v>
+        <v>13.6</v>
       </c>
       <c r="M42" t="n">
-        <v>1.01</v>
+        <v>5.17</v>
       </c>
       <c r="N42" t="n">
         <v>3.17</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>9.9</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45775</v>
+        <v>45776</v>
       </c>
       <c r="H43" t="n">
-        <v>2642.3</v>
+        <v>2797.5</v>
       </c>
       <c r="I43" t="n">
         <v>2778.334718587957</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K43" t="n">
-        <v>-2.46</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="L43" t="n">
-        <v>4.79</v>
+        <v>8.9</v>
       </c>
       <c r="M43" t="n">
         <v>2.96</v>
       </c>
       <c r="N43" t="n">
-        <v>3.91</v>
+        <v>5.87</v>
       </c>
       <c r="O43" t="n">
         <v>-2.21</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>12.96</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45863</v>
+        <v>45866</v>
       </c>
       <c r="H44" t="n">
-        <v>2889</v>
+        <v>2821.6</v>
       </c>
       <c r="I44" t="n">
         <v>2850.160075486879</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K44" t="n">
-        <v>3.27</v>
+        <v>0.86</v>
       </c>
       <c r="L44" t="n">
         <v>5.07</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>9.06</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45881</v>
+        <v>45882</v>
       </c>
       <c r="H45" t="n">
-        <v>3021.7</v>
+        <v>3057.2</v>
       </c>
       <c r="I45" t="n">
         <v>3035.772692635659</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K45" t="n">
-        <v>-7.09</v>
+        <v>-8.35</v>
       </c>
       <c r="L45" t="n">
-        <v>8.09</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="M45" t="n">
         <v>0.75</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>9.039999999999999</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="H46" t="n">
-        <v>3129.1</v>
+        <v>3098.6</v>
       </c>
       <c r="I46" t="n">
         <v>3117.012413813501</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K46" t="n">
-        <v>2.35</v>
+        <v>1.35</v>
       </c>
       <c r="L46" t="n">
         <v>5.23</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>9.119999999999999</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="H47" t="n">
-        <v>2315.7</v>
+        <v>2503.3</v>
       </c>
       <c r="I47" t="n">
         <v>2405.694037193116</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K47" t="n">
-        <v>25.27</v>
+        <v>19.21</v>
       </c>
       <c r="L47" t="n">
         <v>5.3</v>
       </c>
       <c r="M47" t="n">
-        <v>0.85</v>
+        <v>4.33</v>
       </c>
       <c r="N47" t="n">
-        <v>4.17</v>
+        <v>8.1</v>
       </c>
       <c r="O47" t="n">
         <v>-0.97</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>6</v>
+      </c>
+      <c r="U47" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>12.04</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="H48" t="n">
-        <v>2549.7</v>
+        <v>2458.2</v>
       </c>
       <c r="I48" t="n">
         <v>2465.727064414581</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K48" t="n">
-        <v>1.85</v>
+        <v>-1.8</v>
       </c>
       <c r="L48" t="n">
         <v>9.32</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>13.57</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H49" t="n">
-        <v>2588.2</v>
+        <v>2727.1</v>
       </c>
       <c r="I49" t="n">
         <v>2721.012479004406</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K49" t="n">
-        <v>-5.29</v>
+        <v>-10.94</v>
       </c>
       <c r="L49" t="n">
-        <v>9.779999999999999</v>
+        <v>12.19</v>
       </c>
       <c r="M49" t="n">
         <v>4.48</v>
       </c>
       <c r="N49" t="n">
-        <v>4.43</v>
+        <v>5.37</v>
       </c>
       <c r="O49" t="n">
         <v>-3.59</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>13.05</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="H50" t="n">
-        <v>3090.6</v>
+        <v>2975.8</v>
       </c>
       <c r="I50" t="n">
         <v>3011.035911479887</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K50" t="n">
-        <v>13.33</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="L50" t="n">
         <v>2.88</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>4</v>
+      </c>
+      <c r="U50" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -3351,6 +3962,14 @@
       <c r="Q51" t="n">
         <v>81</v>
       </c>
+      <c r="R51" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7153,7 +7772,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>62.7</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="6">
@@ -7163,7 +7782,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7">
@@ -7173,7 +7792,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="8">
@@ -7183,7 +7802,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -7193,7 +7812,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10">
@@ -7203,7 +7822,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>127.4</v>
+        <v>128.4</v>
       </c>
     </row>
     <row r="11">
@@ -7213,7 +7832,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
@@ -7223,7 +7842,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13">
@@ -7233,7 +7852,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>36.7</v>
+        <v>34.7</v>
       </c>
     </row>
     <row r="14">
@@ -7243,7 +7862,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.7</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="15">
@@ -7253,7 +7872,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10.95</v>
+        <v>7.18</v>
       </c>
     </row>
     <row r="16">
@@ -7263,7 +7882,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.23</v>
+        <v>-5.08</v>
       </c>
     </row>
     <row r="17">
@@ -7273,7 +7892,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>69.05</v>
+        <v>56.49</v>
       </c>
     </row>
     <row r="18">
@@ -7283,7 +7902,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>51</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="19">
@@ -7293,7 +7912,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8.42</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -7303,7 +7922,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8.42</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -7313,7 +7932,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>25.75</v>
+        <v>31.87</v>
       </c>
     </row>
     <row r="22">
@@ -7323,7 +7942,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23">
@@ -7333,7 +7952,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
@@ -7343,7 +7962,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.57</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="25">
@@ -7363,7 +7982,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.43</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="27">
@@ -7373,7 +7992,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9.98</v>
+        <v>14.65</v>
       </c>
     </row>
     <row r="28">
@@ -7383,7 +8002,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29">
